--- a/Team-Data/2008-09/2-3-2008-09.xlsx
+++ b/Team-Data/2008-09/2-3-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -751,7 +818,7 @@
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
         <v>23</v>
@@ -763,22 +830,22 @@
         <v>14</v>
       </c>
       <c r="AL2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
         <v>18</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR2" t="n">
         <v>21</v>
@@ -808,10 +875,10 @@
         <v>9</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -858,13 +925,13 @@
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="J3" t="n">
         <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>0.484</v>
+        <v>0.483</v>
       </c>
       <c r="L3" t="n">
         <v>6.6</v>
@@ -873,64 +940,64 @@
         <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>0.391</v>
+        <v>0.389</v>
       </c>
       <c r="O3" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="P3" t="n">
-        <v>26.2</v>
+        <v>26.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.776</v>
+        <v>0.771</v>
       </c>
       <c r="R3" t="n">
         <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T3" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V3" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z3" t="n">
         <v>23.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.6</v>
+        <v>101.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
         <v>13</v>
@@ -951,7 +1018,7 @@
         <v>18</v>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
         <v>7</v>
@@ -960,19 +1027,19 @@
         <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
         <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV3" t="n">
         <v>26</v>
@@ -981,16 +1048,16 @@
         <v>3</v>
       </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
         <v>26</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
@@ -1115,7 +1182,7 @@
         <v>21</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
@@ -1142,10 +1209,10 @@
         <v>18</v>
       </c>
       <c r="AQ4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS4" t="n">
         <v>27</v>
@@ -1160,7 +1227,7 @@
         <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX4" t="n">
         <v>18</v>
@@ -1178,7 +1245,7 @@
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -1210,25 +1277,25 @@
         <v>48</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>0.417</v>
+        <v>0.438</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>84.3</v>
+        <v>83.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
@@ -1237,64 +1304,64 @@
         <v>16.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O5" t="n">
-        <v>18.3</v>
+        <v>18.7</v>
       </c>
       <c r="P5" t="n">
-        <v>23.3</v>
+        <v>23.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.786</v>
+        <v>0.789</v>
       </c>
       <c r="R5" t="n">
         <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U5" t="n">
         <v>21.1</v>
       </c>
       <c r="V5" t="n">
-        <v>14.8</v>
+        <v>15.1</v>
       </c>
       <c r="W5" t="n">
         <v>7.4</v>
       </c>
       <c r="X5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>99.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.6</v>
+        <v>-2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
         <v>5</v>
@@ -1303,10 +1370,10 @@
         <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
         <v>20</v>
@@ -1315,13 +1382,13 @@
         <v>22</v>
       </c>
       <c r="AN5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1339,7 +1406,7 @@
         <v>13</v>
       </c>
       <c r="AV5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
         <v>13</v>
@@ -1348,19 +1415,19 @@
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
         <v>22</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
         <v>12</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -1392,91 +1459,91 @@
         <v>46</v>
       </c>
       <c r="E6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>0.826</v>
+        <v>0.804</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J6" t="n">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="K6" t="n">
         <v>0.476</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.382</v>
+        <v>0.378</v>
       </c>
       <c r="O6" t="n">
         <v>18.7</v>
       </c>
       <c r="P6" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.755</v>
+        <v>0.751</v>
       </c>
       <c r="R6" t="n">
         <v>10.7</v>
       </c>
       <c r="S6" t="n">
-        <v>31</v>
+        <v>31.2</v>
       </c>
       <c r="T6" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U6" t="n">
         <v>20.4</v>
       </c>
       <c r="V6" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
         <v>7.7</v>
       </c>
       <c r="X6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y6" t="n">
         <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.3</v>
+        <v>100.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="AD6" t="n">
         <v>25</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
         <v>24</v>
@@ -1485,28 +1552,28 @@
         <v>9</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO6" t="n">
         <v>19</v>
       </c>
       <c r="AP6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR6" t="n">
         <v>17</v>
@@ -1518,25 +1585,25 @@
         <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW6" t="n">
         <v>9</v>
       </c>
       <c r="AX6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
         <v>5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
         <v>9</v>
@@ -1679,7 +1746,7 @@
         <v>8</v>
       </c>
       <c r="AN7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO7" t="n">
         <v>25</v>
@@ -1700,10 +1767,10 @@
         <v>3</v>
       </c>
       <c r="AU7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
         <v>18</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8" t="n">
         <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>0.667</v>
+        <v>0.66</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
@@ -1771,40 +1838,40 @@
         <v>36.9</v>
       </c>
       <c r="J8" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.471</v>
+        <v>0.472</v>
       </c>
       <c r="L8" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M8" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O8" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="P8" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.757</v>
+        <v>0.755</v>
       </c>
       <c r="R8" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="T8" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="U8" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V8" t="n">
         <v>15.9</v>
@@ -1813,25 +1880,25 @@
         <v>9.1</v>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y8" t="n">
         <v>5.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="AB8" t="n">
         <v>104.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
@@ -1843,13 +1910,13 @@
         <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AJ8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1861,7 +1928,7 @@
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR8" t="n">
         <v>22</v>
@@ -1882,7 +1949,7 @@
         <v>16</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV8" t="n">
         <v>28</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -2055,13 +2122,13 @@
         <v>25</v>
       </c>
       <c r="AR9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU9" t="n">
         <v>24</v>
@@ -2079,10 +2146,10 @@
         <v>4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
         <v>29</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>25</v>
@@ -2234,10 +2301,10 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS10" t="n">
         <v>14</v>
@@ -2249,7 +2316,7 @@
         <v>17</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW10" t="n">
         <v>7</v>
@@ -2258,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
         <v>19</v>
       </c>
       <c r="G11" t="n">
-        <v>0.612</v>
+        <v>0.604</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
@@ -2317,28 +2384,28 @@
         <v>35.5</v>
       </c>
       <c r="J11" t="n">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="K11" t="n">
         <v>0.445</v>
       </c>
       <c r="L11" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M11" t="n">
         <v>20.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O11" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P11" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.806</v>
+        <v>0.804</v>
       </c>
       <c r="R11" t="n">
         <v>10.6</v>
@@ -2353,13 +2420,13 @@
         <v>20.3</v>
       </c>
       <c r="V11" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W11" t="n">
         <v>6.7</v>
       </c>
       <c r="X11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Y11" t="n">
         <v>5.5</v>
@@ -2371,16 +2438,16 @@
         <v>21.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC11" t="n">
         <v>2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF11" t="n">
         <v>9</v>
@@ -2410,16 +2477,16 @@
         <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AP11" t="n">
         <v>19</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
         <v>3</v>
@@ -2428,19 +2495,19 @@
         <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV11" t="n">
         <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX11" t="n">
         <v>29</v>
       </c>
       <c r="AY11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -2481,97 +2548,97 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E12" t="n">
         <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G12" t="n">
-        <v>0.388</v>
+        <v>0.396</v>
       </c>
       <c r="H12" t="n">
         <v>48.6</v>
       </c>
       <c r="I12" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J12" t="n">
-        <v>86.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="K12" t="n">
         <v>0.452</v>
       </c>
       <c r="L12" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M12" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.368</v>
+        <v>0.366</v>
       </c>
       <c r="O12" t="n">
         <v>19.1</v>
       </c>
       <c r="P12" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.803</v>
+        <v>0.806</v>
       </c>
       <c r="R12" t="n">
         <v>11.3</v>
       </c>
       <c r="S12" t="n">
-        <v>32.2</v>
+        <v>32.4</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U12" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V12" t="n">
         <v>15.2</v>
       </c>
       <c r="W12" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y12" t="n">
         <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AA12" t="n">
         <v>21.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.8</v>
+        <v>104.7</v>
       </c>
       <c r="AC12" t="n">
         <v>-2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI12" t="n">
         <v>2</v>
@@ -2583,10 +2650,10 @@
         <v>16</v>
       </c>
       <c r="AL12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN12" t="n">
         <v>16</v>
@@ -2598,7 +2665,7 @@
         <v>20</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR12" t="n">
         <v>13</v>
@@ -2616,16 +2683,16 @@
         <v>23</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
         <v>12</v>
@@ -2634,7 +2701,7 @@
         <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
         <v>29</v>
@@ -2765,7 +2832,7 @@
         <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM13" t="n">
         <v>17</v>
@@ -2780,7 +2847,7 @@
         <v>25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR13" t="n">
         <v>11</v>
@@ -2795,7 +2862,7 @@
         <v>22</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
         <v>19</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14" t="n">
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>0.804</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="J14" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K14" t="n">
         <v>0.479</v>
@@ -2872,28 +2939,28 @@
         <v>7.1</v>
       </c>
       <c r="M14" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.374</v>
+        <v>0.378</v>
       </c>
       <c r="O14" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="P14" t="n">
-        <v>27.7</v>
+        <v>27.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R14" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S14" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="T14" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U14" t="n">
         <v>23.3</v>
@@ -2905,43 +2972,43 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y14" t="n">
         <v>4.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>109</v>
+        <v>108.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="n">
         <v>2</v>
       </c>
-      <c r="AG14" t="n">
-        <v>3</v>
-      </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK14" t="n">
         <v>3</v>
@@ -2953,22 +3020,22 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
       </c>
       <c r="AP14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR14" t="n">
         <v>4</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2986,13 +3053,13 @@
         <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,7 +3184,7 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI15" t="n">
         <v>29</v>
@@ -3138,13 +3205,13 @@
         <v>27</v>
       </c>
       <c r="AO15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP15" t="n">
         <v>9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR15" t="n">
         <v>25</v>
@@ -3159,7 +3226,7 @@
         <v>30</v>
       </c>
       <c r="AV15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW15" t="n">
         <v>8</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
         <v>13</v>
@@ -3302,7 +3369,7 @@
         <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ16" t="n">
         <v>13</v>
@@ -3326,7 +3393,7 @@
         <v>22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR16" t="n">
         <v>24</v>
@@ -3347,10 +3414,10 @@
         <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ16" t="n">
         <v>13</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -3406,46 +3473,46 @@
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>36.3</v>
+        <v>36.5</v>
       </c>
       <c r="J17" t="n">
         <v>81.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.447</v>
+        <v>0.449</v>
       </c>
       <c r="L17" t="n">
         <v>5.6</v>
       </c>
       <c r="M17" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="P17" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.785</v>
+        <v>0.786</v>
       </c>
       <c r="R17" t="n">
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U17" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V17" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W17" t="n">
         <v>7.1</v>
@@ -3457,13 +3524,13 @@
         <v>4.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>98.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="AC17" t="n">
         <v>0.2</v>
@@ -3484,13 +3551,13 @@
         <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AJ17" t="n">
         <v>12</v>
       </c>
       <c r="AK17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
         <v>23</v>
@@ -3499,46 +3566,46 @@
         <v>23</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>9</v>
       </c>
       <c r="AR17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS17" t="n">
         <v>22</v>
       </c>
       <c r="AT17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV17" t="n">
         <v>16</v>
       </c>
       <c r="AW17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX17" t="n">
         <v>28</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB17" t="n">
         <v>17</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -3573,52 +3640,52 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F18" t="n">
         <v>30</v>
       </c>
       <c r="G18" t="n">
-        <v>0.362</v>
+        <v>0.348</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
       </c>
       <c r="I18" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J18" t="n">
         <v>83.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L18" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M18" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.343</v>
+        <v>0.339</v>
       </c>
       <c r="O18" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P18" t="n">
         <v>25</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.772</v>
+        <v>0.769</v>
       </c>
       <c r="R18" t="n">
         <v>12.4</v>
       </c>
       <c r="S18" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T18" t="n">
         <v>42.2</v>
@@ -3627,10 +3694,10 @@
         <v>20.6</v>
       </c>
       <c r="V18" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W18" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X18" t="n">
         <v>4.2</v>
@@ -3645,19 +3712,19 @@
         <v>20.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>99.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
         <v>24</v>
       </c>
       <c r="AF18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG18" t="n">
         <v>24</v>
@@ -3666,7 +3733,7 @@
         <v>9</v>
       </c>
       <c r="AI18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>6</v>
@@ -3675,22 +3742,22 @@
         <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM18" t="n">
         <v>20</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP18" t="n">
         <v>15</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR18" t="n">
         <v>3</v>
@@ -3702,16 +3769,16 @@
         <v>12</v>
       </c>
       <c r="AU18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV18" t="n">
         <v>15</v>
       </c>
       <c r="AW18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY18" t="n">
         <v>30</v>
@@ -3720,7 +3787,7 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
         <v>14</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F19" t="n">
         <v>27</v>
       </c>
       <c r="G19" t="n">
-        <v>0.449</v>
+        <v>0.438</v>
       </c>
       <c r="H19" t="n">
         <v>48.6</v>
@@ -3773,7 +3840,7 @@
         <v>35.3</v>
       </c>
       <c r="J19" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="K19" t="n">
         <v>0.44</v>
@@ -3785,7 +3852,7 @@
         <v>20.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0.378</v>
+        <v>0.376</v>
       </c>
       <c r="O19" t="n">
         <v>19.5</v>
@@ -3794,7 +3861,7 @@
         <v>25.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.776</v>
+        <v>0.774</v>
       </c>
       <c r="R19" t="n">
         <v>11.2</v>
@@ -3803,16 +3870,16 @@
         <v>29.5</v>
       </c>
       <c r="T19" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U19" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="V19" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W19" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X19" t="n">
         <v>4.5</v>
@@ -3830,10 +3897,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.8</v>
+        <v>-3.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
@@ -3842,16 +3909,16 @@
         <v>18</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI19" t="n">
         <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK19" t="n">
         <v>29</v>
@@ -3860,16 +3927,16 @@
         <v>6</v>
       </c>
       <c r="AM19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO19" t="n">
         <v>11</v>
       </c>
       <c r="AP19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ19" t="n">
         <v>11</v>
@@ -3890,13 +3957,13 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX19" t="n">
         <v>21</v>
       </c>
       <c r="AY19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ19" t="n">
         <v>27</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4088,7 @@
         <v>9</v>
       </c>
       <c r="AF20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG20" t="n">
         <v>8</v>
@@ -4039,13 +4106,13 @@
         <v>13</v>
       </c>
       <c r="AL20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM20" t="n">
         <v>11</v>
       </c>
       <c r="AN20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO20" t="n">
         <v>24</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -4197,19 +4264,19 @@
         <v>-2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF21" t="n">
         <v>17</v>
       </c>
       <c r="AG21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI21" t="n">
         <v>7</v>
@@ -4242,10 +4309,10 @@
         <v>15</v>
       </c>
       <c r="AS21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU21" t="n">
         <v>9</v>
@@ -4263,7 +4330,7 @@
         <v>21</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>27</v>
@@ -4394,13 +4461,13 @@
         <v>12</v>
       </c>
       <c r="AI22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ22" t="n">
         <v>11</v>
       </c>
       <c r="AK22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4409,16 +4476,16 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP22" t="n">
         <v>8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR22" t="n">
         <v>7</v>
@@ -4445,7 +4512,7 @@
         <v>22</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA22" t="n">
         <v>17</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>8.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,7 +4640,7 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI23" t="n">
         <v>18</v>
@@ -4582,7 +4649,7 @@
         <v>21</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4594,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="AO23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AP23" t="n">
         <v>6</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G24" t="n">
-        <v>0.489</v>
+        <v>0.5</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
@@ -4692,34 +4759,34 @@
         <v>4.3</v>
       </c>
       <c r="M24" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0.325</v>
+        <v>0.328</v>
       </c>
       <c r="O24" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P24" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.743</v>
+        <v>0.741</v>
       </c>
       <c r="R24" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S24" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="T24" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="U24" t="n">
         <v>20.6</v>
       </c>
       <c r="V24" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W24" t="n">
         <v>8</v>
@@ -4728,22 +4795,22 @@
         <v>5.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB24" t="n">
         <v>96.40000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE24" t="n">
         <v>17</v>
@@ -4755,13 +4822,13 @@
         <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
         <v>14</v>
       </c>
       <c r="AJ24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK24" t="n">
         <v>10</v>
@@ -4776,13 +4843,13 @@
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ24" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AR24" t="n">
         <v>2</v>
@@ -4791,10 +4858,10 @@
         <v>16</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AU24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV24" t="n">
         <v>24</v>
@@ -4812,7 +4879,7 @@
         <v>8</v>
       </c>
       <c r="BA24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB24" t="n">
         <v>24</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -4961,19 +5028,19 @@
         <v>5</v>
       </c>
       <c r="AP25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR25" t="n">
         <v>27</v>
       </c>
       <c r="AS25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU25" t="n">
         <v>7</v>
@@ -4985,7 +5052,7 @@
         <v>29</v>
       </c>
       <c r="AX25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY25" t="n">
         <v>6</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E26" t="n">
         <v>30</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>0.652</v>
+        <v>0.638</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.462</v>
+        <v>0.459</v>
       </c>
       <c r="L26" t="n">
         <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O26" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="P26" t="n">
-        <v>25.5</v>
+        <v>25.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.764</v>
+        <v>0.761</v>
       </c>
       <c r="R26" t="n">
         <v>13.2</v>
@@ -5083,37 +5150,37 @@
         <v>20.3</v>
       </c>
       <c r="V26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W26" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X26" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.2</v>
+        <v>98.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AD26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="n">
         <v>7</v>
@@ -5122,13 +5189,13 @@
         <v>11</v>
       </c>
       <c r="AI26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AJ26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
@@ -5140,13 +5207,13 @@
         <v>8</v>
       </c>
       <c r="AO26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5158,10 +5225,10 @@
         <v>17</v>
       </c>
       <c r="AU26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW26" t="n">
         <v>21</v>
@@ -5173,13 +5240,13 @@
         <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA26" t="n">
         <v>11</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5371,7 @@
         <v>4</v>
       </c>
       <c r="AI27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ27" t="n">
         <v>10</v>
@@ -5319,13 +5386,13 @@
         <v>14</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO27" t="n">
         <v>6</v>
       </c>
       <c r="AP27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ27" t="n">
         <v>4</v>
@@ -5346,13 +5413,13 @@
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX27" t="n">
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ27" t="n">
         <v>30</v>
@@ -5361,7 +5428,7 @@
         <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E28" t="n">
         <v>33</v>
       </c>
       <c r="F28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.702</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
@@ -5411,67 +5478,67 @@
         <v>36.9</v>
       </c>
       <c r="J28" t="n">
-        <v>79.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
       <c r="L28" t="n">
         <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N28" t="n">
         <v>0.392</v>
       </c>
       <c r="O28" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P28" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="R28" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T28" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U28" t="n">
         <v>21.9</v>
       </c>
       <c r="V28" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="W28" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="X28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB28" t="n">
         <v>97.59999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5486,7 +5553,7 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ28" t="n">
         <v>18</v>
@@ -5510,16 +5577,16 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -5531,10 +5598,10 @@
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -5575,61 +5642,61 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
         <v>19</v>
       </c>
       <c r="F29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>0.38</v>
+        <v>0.388</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J29" t="n">
         <v>78.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.459</v>
+        <v>0.461</v>
       </c>
       <c r="L29" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M29" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.375</v>
+        <v>0.379</v>
       </c>
       <c r="O29" t="n">
         <v>19.1</v>
       </c>
       <c r="P29" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.824</v>
+        <v>0.825</v>
       </c>
       <c r="R29" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S29" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T29" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="U29" t="n">
         <v>21.7</v>
       </c>
       <c r="V29" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W29" t="n">
         <v>6.5</v>
@@ -5641,25 +5708,25 @@
         <v>4.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.2</v>
+        <v>97.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.8</v>
+        <v>-2.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
       </c>
       <c r="AF29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG29" t="n">
         <v>23</v>
@@ -5668,13 +5735,13 @@
         <v>19</v>
       </c>
       <c r="AI29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AL29" t="n">
         <v>19</v>
@@ -5683,7 +5750,7 @@
         <v>21</v>
       </c>
       <c r="AN29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AO29" t="n">
         <v>16</v>
@@ -5707,10 +5774,10 @@
         <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX29" t="n">
         <v>16</v>
@@ -5722,7 +5789,7 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB29" t="n">
         <v>21</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>2.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>11</v>
@@ -5856,7 +5923,7 @@
         <v>16</v>
       </c>
       <c r="AK30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL30" t="n">
         <v>26</v>
@@ -5889,7 +5956,7 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-7.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6032,7 +6099,7 @@
         <v>29</v>
       </c>
       <c r="AI31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ31" t="n">
         <v>9</v>
@@ -6056,7 +6123,7 @@
         <v>28</v>
       </c>
       <c r="AQ31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR31" t="n">
         <v>10</v>
@@ -6068,7 +6135,7 @@
         <v>24</v>
       </c>
       <c r="AU31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV31" t="n">
         <v>12</v>
@@ -6083,7 +6150,7 @@
         <v>17</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-3-2008-09</t>
+          <t>2009-02-03</t>
         </is>
       </c>
     </row>
